--- a/src/synth/New Microsoft Excel Worksheet.xlsx
+++ b/src/synth/New Microsoft Excel Worksheet.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\reserach\RV32I-Pipeline\src\synth\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBDACE3-F7AF-48D7-823F-84B4071B3ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,15 +24,216 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+  <si>
+    <t>Worst setup slack (ns)</t>
+  </si>
+  <si>
+    <t>Timing status</t>
+  </si>
+  <si>
+    <t>Total cell area (µm²)</t>
+  </si>
+  <si>
+    <t>Cells</t>
+  </si>
+  <si>
+    <t>Dynamic (µW)</t>
+  </si>
+  <si>
+    <t>Leakage (µW)</t>
+  </si>
+  <si>
+    <t>−0.0234</t>
+  </si>
+  <si>
+    <t>Violated</t>
+  </si>
+  <si>
+    <t>15 304.58</t>
+  </si>
+  <si>
+    <t>−0.0439</t>
+  </si>
+  <si>
+    <t>15 317.08</t>
+  </si>
+  <si>
+    <t>Met (marginal)</t>
+  </si>
+  <si>
+    <t>15 265.74</t>
+  </si>
+  <si>
+    <t>Met</t>
+  </si>
+  <si>
+    <t>15 221.58</t>
+  </si>
+  <si>
+    <t>15 182.75</t>
+  </si>
+  <si>
+    <t>15 087.25</t>
+  </si>
+  <si>
+    <r>
+      <t>Tclk</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13.3"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7.7"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>clk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="1"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t> (ns)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>fclk</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13.3"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>f</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7.7"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>clk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="1"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t> (MHz)</t>
+    </r>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14.3"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13.3"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13.3"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="13.3"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7.7"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="1"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +244,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +252,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +576,215 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BFA4B8-0673-442B-9476-14D0E9908750}">
+  <dimension ref="A3:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>10</v>
+      </c>
+      <c r="B7" s="7">
+        <v>100</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="7">
+        <v>6913</v>
+      </c>
+      <c r="G7" s="7">
+        <v>832.8</v>
+      </c>
+      <c r="H7" s="7">
+        <v>54.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>11</v>
+      </c>
+      <c r="B8" s="7">
+        <v>90.9</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="7">
+        <v>6929</v>
+      </c>
+      <c r="G8" s="7">
+        <v>757.25</v>
+      </c>
+      <c r="H8" s="7">
+        <v>54.35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>12</v>
+      </c>
+      <c r="B9" s="7">
+        <v>83.3</v>
+      </c>
+      <c r="C9" s="7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="7">
+        <v>6820</v>
+      </c>
+      <c r="G9" s="7">
+        <v>693.54</v>
+      </c>
+      <c r="H9" s="7">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>13</v>
+      </c>
+      <c r="B10" s="7">
+        <v>76.900000000000006</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.16109999999999999</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="7">
+        <v>6747</v>
+      </c>
+      <c r="G10" s="7">
+        <v>640.25</v>
+      </c>
+      <c r="H10" s="7">
+        <v>53.53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>15</v>
+      </c>
+      <c r="B11" s="7">
+        <v>66.7</v>
+      </c>
+      <c r="C11" s="7">
+        <v>4.6699999999999998E-2</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="7">
+        <v>7008</v>
+      </c>
+      <c r="G11" s="7">
+        <v>554.97</v>
+      </c>
+      <c r="H11" s="7">
+        <v>52.34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>20</v>
+      </c>
+      <c r="B12" s="7">
+        <v>50</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.36649999999999999</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="7">
+        <v>7928</v>
+      </c>
+      <c r="G12" s="7">
+        <v>415.93</v>
+      </c>
+      <c r="H12" s="7">
+        <v>50.42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>